--- a/docs/ai-caiq/AI-CAIQ-spindlebox-v1.1.0.xlsx
+++ b/docs/ai-caiq/AI-CAIQ-spindlebox-v1.1.0.xlsx
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="D219" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D220" s="18" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E220" s="18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="D229" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E229" s="14" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D231" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E231" s="14" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D282" s="18" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E282" s="18" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="D283" s="14" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>Owned by OSP</t>
         </is>
       </c>
       <c r="E283" s="14" t="inlineStr">
